--- a/SuppXLS/Scen_RES_SHARE_50%_ANNUAL.xlsx
+++ b/SuppXLS/Scen_RES_SHARE_50%_ANNUAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr codeName="Ten_skoroszyt" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda2\Veda_models\MSc_SELECT_2026\MSc_SELECT-main\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\juane\Documents\Master UPC\2 Energy Modelling and Climate Policy\TIMES Project\Msc_SELECT_VEDA\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDAC8148-7458-4C19-BBD4-8813B89858F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90224A4F-18F7-4167-BF25-28CEE623EF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COM_BND" sheetId="1" r:id="rId1"/>
@@ -65,9 +65,6 @@
   </si>
   <si>
     <t>ELC_GRID_RES</t>
-  </si>
-  <si>
-    <t>FX</t>
   </si>
   <si>
     <t>\I: Name of the constraint</t>
@@ -178,6 +175,9 @@
       </rPr>
       <t xml:space="preserve"> NL</t>
     </r>
+  </si>
+  <si>
+    <t>LO</t>
   </si>
 </sst>
 </file>
@@ -7194,26 +7194,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Arkusz1"/>
   <dimension ref="B2:U30"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.5703125" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" customWidth="1"/>
-    <col min="8" max="10" width="12.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.85546875" customWidth="1"/>
-    <col min="12" max="15" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="8" max="10" width="12.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.88671875" customWidth="1"/>
+    <col min="12" max="15" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:21" ht="15" customHeight="1">
       <c r="B2" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9"/>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="3" spans="2:21" ht="15" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -7257,7 +7257,7 @@
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
     </row>
-    <row r="6" spans="2:21" ht="31.7" customHeight="1">
+    <row r="6" spans="2:21" ht="31.65" customHeight="1">
       <c r="B6" s="13" t="s">
         <v>1</v>
       </c>
@@ -7274,19 +7274,19 @@
         <v>5</v>
       </c>
       <c r="G6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="I6" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I6" s="14" t="s">
+      <c r="J6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="K6" s="14" t="s">
         <v>32</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>33</v>
       </c>
       <c r="L6" s="14" t="s">
         <v>6</v>
@@ -7297,32 +7297,32 @@
     </row>
     <row r="7" spans="2:21" ht="47.25" customHeight="1" thickBot="1">
       <c r="B7" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="G7" s="31" t="s">
         <v>16</v>
-      </c>
-      <c r="G7" s="31" t="s">
-        <v>17</v>
       </c>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="J7" s="31"/>
       <c r="K7" s="31"/>
       <c r="L7" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="2:21" ht="42" customHeight="1" thickBot="1">
@@ -7336,7 +7336,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="F8" s="12">
         <v>1</v>
@@ -7371,7 +7371,7 @@
     </row>
     <row r="17" spans="3:11">
       <c r="D17" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="3:11">
@@ -7380,7 +7380,7 @@
     </row>
     <row r="20" spans="3:11">
       <c r="D20" s="19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E20" s="20">
         <v>2023</v>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="21" spans="3:11" ht="38.25" customHeight="1">
       <c r="D21" s="21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E21" s="32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F21" s="32"/>
       <c r="G21" s="32"/>
@@ -7420,7 +7420,7 @@
     </row>
     <row r="22" spans="3:11">
       <c r="D22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E22" s="22">
         <f t="shared" ref="E22:K22" si="1">E27*3.6</f>
@@ -7462,7 +7462,7 @@
     </row>
     <row r="24" spans="3:11">
       <c r="E24" s="24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F24" s="23"/>
       <c r="G24" s="23"/>
@@ -7505,7 +7505,7 @@
     </row>
     <row r="27" spans="3:11">
       <c r="D27" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" s="26">
         <v>109.39</v>
@@ -7535,13 +7535,13 @@
     </row>
     <row r="29" spans="3:11">
       <c r="E29" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="3:11">
       <c r="E30" s="29"/>
       <c r="F30" s="25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -7558,15 +7558,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100A7D98A4600D5044F9F854C890D6CC50E" ma:contentTypeVersion="12" ma:contentTypeDescription="Utwórz nowy dokument." ma:contentTypeScope="" ma:versionID="5ae10a33478425c8b0682342cd902bb6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8acd6055-54fc-4ce7-b3df-0a09834a0329" xmlns:ns3="708d6b01-37ca-4db4-bc7f-9b68f32c58b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d4d464c5e04a95514152bf5b8c9c7854" ns2:_="" ns3:_="">
     <xsd:import namespace="8acd6055-54fc-4ce7-b3df-0a09834a0329"/>
@@ -7785,6 +7776,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7797,14 +7797,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F91B0505-87C0-4533-9D1B-20F030974763}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9690AA4-2973-4C8B-AFF5-174A0EBF4012}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7823,6 +7815,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F91B0505-87C0-4533-9D1B-20F030974763}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1414681-578E-43B8-8934-BC5759CBC3B5}">
   <ds:schemaRefs>
